--- a/SeleniumTests/TestDataFolder/SettingOnDashboardTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/SettingOnDashboardTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1546E1C8-CFF4-4C07-935D-F580569EB95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE63BB-BCD0-43DD-99A3-E9D0D2DA5E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="InvalidFile_Dashboard" sheetId="2" r:id="rId1"/>
@@ -39,15 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
-    <t>CutOffDate</t>
-  </si>
-  <si>
-    <t>ConsolidateCutOffDate</t>
-  </si>
-  <si>
-    <t>securityToken</t>
-  </si>
-  <si>
     <t>true</t>
   </si>
   <si>
@@ -57,7 +48,16 @@
     <t>@"D:\e-invoice\SeleniumTests\ReceiptTest.txt"</t>
   </si>
   <si>
-    <t>filepath</t>
+    <t>B2C Convrsion Cut Off Date</t>
+  </si>
+  <si>
+    <t>Auto Consolidate Cut Off Date</t>
+  </si>
+  <si>
+    <t>Security Token (true/false)</t>
+  </si>
+  <si>
+    <t>Import File Path</t>
   </si>
 </sst>
 </file>
@@ -378,16 +378,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC7FE8C-1496-4653-84CD-9866C387AD7A}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -401,10 +407,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -416,16 +422,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07940A1-0A90-4C62-A863-B99850D47459}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -439,10 +451,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
